--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/预集成预验证需求信息表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/预集成预验证需求信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>第6章修复校验</t>
+          <t>昇腾 ATLAS A3 900 Superpod*1 CCAE V1R2 版本未确认</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -467,7 +467,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260613</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -480,25 +480,81 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
+          <t>DT 950 产品系列与 HCS V1R2 物认匹配</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ATALAS A3 产品本身移动九天平台 KBS 兼容性测试</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>第6章修复校验</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>TD</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>20260613</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
         </is>
